--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24751.65</v>
+        <v>24274.9</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50956.5</v>
+        <v>50705.23</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30032.48</v>
+        <v>29953.39</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8271.790000000001</v>
+        <v>8225.639999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7447.02</v>
+        <v>7281.52</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38885.37</v>
+        <v>38950.97</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12911.13</v>
+        <v>13000.53</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13590.55</v>
+        <v>13696.83</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18884.16</v>
+        <v>18625.2</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>132104.82</v>
+        <v>133390.47</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>15789.24</v>
+        <v>15606.73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2743-1-CM26</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24274.9</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2546-46-CM26</t>
+          <t>2743-1-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50705.23</v>
+        <v>24274.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2546-25-CM26</t>
+          <t>2546-46-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29953.39</v>
+        <v>50705.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057387-150-CM26</t>
+          <t>2546-25-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8225.639999999999</v>
+        <v>29953.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3808-38-CM26</t>
+          <t>1057387-150-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ADOLFO IGNACIO</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.707.293-7</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7281.52</v>
+        <v>8225.639999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5586-1200-CM26</t>
+          <t>3808-38-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>ADOLFO IGNACIO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
+          <t>76.707.293-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38950.97</v>
+        <v>7281.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2387-222-CM26</t>
+          <t>5586-1200-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>76.572.009-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13000.53</v>
+        <v>38950.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3708-183-CM26</t>
+          <t>2387-222-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.504.980-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13696.83</v>
+        <v>13000.53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>765-144-CM26</t>
+          <t>3708-183-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18625.2</v>
+        <v>13696.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5586-761-CM26</t>
+          <t>765-144-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>133390.47</v>
+        <v>18625.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>5586-761-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,6 +1179,67 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
+        <v>133390.47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>765-158-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>15606.73</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>765-409-CM25</t>
+          <t>1175-133-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>37572.09</v>
+        <v>50825.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2743-1-CM26</t>
+          <t>1175-147-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24274.9</v>
+        <v>41533.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2546-46-CM26</t>
+          <t>2546-20-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>50705.23</v>
+        <v>26330.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2546-25-CM26</t>
+          <t>765-316-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>MICROSYSTEM S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>94.099.000-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29953.39</v>
+        <v>132651.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057387-150-CM26</t>
+          <t>765-349-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8225.639999999999</v>
+        <v>10590.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3808-38-CM26</t>
+          <t>986278-204-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ADOLFO IGNACIO</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.707.293-7</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7281.52</v>
+        <v>6702.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5586-1200-CM26</t>
+          <t>722-158-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38950.97</v>
+        <v>25422.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2387-222-CM26</t>
+          <t>765-406-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13000.53</v>
+        <v>14785.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3708-183-CM26</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13696.83</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>765-144-CM26</t>
+          <t>2743-1-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18625.2</v>
+        <v>24274.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5586-761-CM26</t>
+          <t>2546-46-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>133390.47</v>
+        <v>50705.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>2546-25-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,556 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
+        <v>29953.39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1057387-150-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.602.223-7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Asimov Consultores SpA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.372.725-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>8225.639999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3808-38-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.180.200-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUREN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ADOLFO IGNACIO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.707.293-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>7281.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5586-1200-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IMPACTE SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>38950.97</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2387-222-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ESRI CHILE S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>13000.53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3708-183-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>VICTORIA SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>13696.83</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>765-144-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>18625.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5586-761-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>133390.47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>765-158-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>15606.73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>765-174-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RIALIS SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.348.639-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>31171.73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ADOLFO IGNACIO</t>
+          <t>Adolfo Ignacio</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1790,6 +1790,67 @@
       </c>
       <c r="M22" s="2" t="n">
         <v>31171.73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>765-194-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>RIALIS SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.348.639-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>14788.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -697,7 +701,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>765-316-CM25</t>
+          <t>2036-255-SE25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +711,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +726,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.602.247-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SERVICIO DE SALUD DE LA ARAUCANIA SUR HOSPITAL LONCOCHE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,28 +741,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MICROSYSTEM S.A.</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>94.099.000-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>132651.46</v>
+        <v>14113.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>765-349-CM25</t>
+          <t>765-316-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +776,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>MICROSYSTEM S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>94.099.000-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10590.65</v>
+        <v>132651.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>986278-204-CM25</t>
+          <t>765-349-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +842,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +867,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6702.97</v>
+        <v>10590.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>722-158-CM25</t>
+          <t>986278-204-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +907,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +917,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +932,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +947,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25422.25</v>
+        <v>6702.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>765-406-CM25</t>
+          <t>722-158-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +963,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +1008,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14785.64</v>
+        <v>25422.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>765-409-CM25</t>
+          <t>765-406-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1029,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1042,12 +1054,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1069,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>37572.09</v>
+        <v>14785.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2743-1-CM26</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1085,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,28 +1115,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>24274.9</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2546-46-CM26</t>
+          <t>2743-1-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1150,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1165,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1180,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>50705.23</v>
+        <v>24274.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2546-25-CM26</t>
+          <t>2546-46-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1220,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,12 +1245,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1260,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>29953.39</v>
+        <v>50705.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057387-150-CM26</t>
+          <t>2546-25-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1276,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1291,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1306,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1321,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8225.639999999999</v>
+        <v>29953.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3808-38-CM26</t>
+          <t>1057387-150-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1337,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1352,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1367,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Adolfo Ignacio</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.707.293-7</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1382,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7281.52</v>
+        <v>8225.639999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5586-1200-CM26</t>
+          <t>3808-38-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1398,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1413,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1428,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>Adolfo Ignacio</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
+          <t>76.707.293-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1443,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38950.97</v>
+        <v>7281.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2387-222-CM26</t>
+          <t>5586-1200-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1464,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1474,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1489,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13000.53</v>
+        <v>38950.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3708-183-CM26</t>
+          <t>2387-222-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1529,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1539,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1554,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13696.83</v>
+        <v>13000.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>765-144-CM26</t>
+          <t>3708-183-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1589,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1604,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,28 +1619,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>18625.2</v>
+        <v>13696.83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5586-761-CM26</t>
+          <t>2036-296-SE26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1654,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.602.247-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SERVICIO DE SALUD DE LA ARAUCANIA SUR HOSPITAL LONCOCHE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1684,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>133390.47</v>
+        <v>15302.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>765-144-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1719,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1713,28 +1749,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15606.73</v>
+        <v>18625.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>765-174-CM26</t>
+          <t>5586-761-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1784,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1799,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,82 +1814,212 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>31171.73</v>
+        <v>133390.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>765-158-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>15606.73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>765-174-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RIALIS SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.348.639-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>31171.73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>765-194-CM26</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>72.396.000-2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>RIALIS SPA</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>76.348.639-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>14788.38</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/araucania.xlsx
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
